--- a/Data Files/Backoffce/IndexacaoFG/IndexacaoFG - RODAR - Copia (2).xlsx
+++ b/Data Files/Backoffce/IndexacaoFG/IndexacaoFG - RODAR - Copia (2).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Public\RPA_ALLIANZ_TREINAMENTO\Data Files\Backoffce\IndexacaoFG\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9D16B3-C6B3-49F4-BB48-89848068B4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CB79368-2A61-489C-80E3-3FE6C1872661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="1515" windowWidth="15375" windowHeight="7875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IndexacaoFG" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="33">
   <si>
     <t xml:space="preserve">status </t>
   </si>
@@ -51,157 +51,82 @@
     <t>Processar</t>
   </si>
   <si>
-    <t>Relatório Recusa _ SICREDI_04.08.2025</t>
-  </si>
-  <si>
-    <t>130559298</t>
-  </si>
-  <si>
-    <t>971</t>
-  </si>
-  <si>
-    <t>Recusas Sicredi 04/08/2025</t>
-  </si>
-  <si>
-    <t>133562901</t>
-  </si>
-  <si>
-    <t>133569811</t>
-  </si>
-  <si>
-    <t>133615503</t>
-  </si>
-  <si>
-    <t>133625116</t>
-  </si>
-  <si>
-    <t>133651583</t>
-  </si>
-  <si>
-    <t>133661946</t>
-  </si>
-  <si>
-    <t>133660538</t>
-  </si>
-  <si>
-    <t>133674181</t>
-  </si>
-  <si>
-    <t>133682897</t>
-  </si>
-  <si>
-    <t>133695571</t>
-  </si>
-  <si>
-    <t>133693020</t>
-  </si>
-  <si>
-    <t>133681924</t>
-  </si>
-  <si>
-    <t>133687082</t>
-  </si>
-  <si>
-    <t>133716191</t>
-  </si>
-  <si>
-    <t>133716437</t>
-  </si>
-  <si>
-    <t>133704092</t>
-  </si>
-  <si>
-    <t>133708709</t>
-  </si>
-  <si>
-    <t>133723148</t>
-  </si>
-  <si>
-    <t>133728605</t>
-  </si>
-  <si>
-    <t>133706341</t>
-  </si>
-  <si>
-    <t>133735676</t>
-  </si>
-  <si>
-    <t>133740147</t>
-  </si>
-  <si>
-    <t>133739560</t>
-  </si>
-  <si>
-    <t>133742066</t>
-  </si>
-  <si>
-    <t>133725816</t>
-  </si>
-  <si>
-    <t>131847875</t>
-  </si>
-  <si>
-    <t>133596187</t>
-  </si>
-  <si>
-    <t>133621197</t>
-  </si>
-  <si>
-    <t>133657697</t>
-  </si>
-  <si>
-    <t>133750820</t>
-  </si>
-  <si>
-    <t>131000309</t>
-  </si>
-  <si>
-    <t>133689520</t>
-  </si>
-  <si>
-    <t>133756330</t>
-  </si>
-  <si>
-    <t>133759830</t>
-  </si>
-  <si>
-    <t>133543009</t>
-  </si>
-  <si>
-    <t>133618708</t>
-  </si>
-  <si>
-    <t>133619290</t>
-  </si>
-  <si>
-    <t>133761593</t>
-  </si>
-  <si>
-    <t>133624244</t>
-  </si>
-  <si>
-    <t>133564674</t>
-  </si>
-  <si>
-    <t>133627732</t>
-  </si>
-  <si>
-    <t>133547546</t>
-  </si>
-  <si>
-    <t>133758332</t>
-  </si>
-  <si>
-    <t>133630014</t>
-  </si>
-  <si>
-    <t>133631665</t>
-  </si>
-  <si>
-    <t>133595155</t>
-  </si>
-  <si>
-    <t>133585778</t>
+    <t>133660757</t>
+  </si>
+  <si>
+    <t>1070</t>
+  </si>
+  <si>
+    <t>Relatório Recusas Santander- 06/08/2025</t>
+  </si>
+  <si>
+    <t>133686941</t>
+  </si>
+  <si>
+    <t>133689409</t>
+  </si>
+  <si>
+    <t>133684521</t>
+  </si>
+  <si>
+    <t>133752220</t>
+  </si>
+  <si>
+    <t>133757621</t>
+  </si>
+  <si>
+    <t>133667865</t>
+  </si>
+  <si>
+    <t>133786192</t>
+  </si>
+  <si>
+    <t>133785990</t>
+  </si>
+  <si>
+    <t>133597824</t>
+  </si>
+  <si>
+    <t>133601530</t>
+  </si>
+  <si>
+    <t>133684364</t>
+  </si>
+  <si>
+    <t>133602003</t>
+  </si>
+  <si>
+    <t>133657516</t>
+  </si>
+  <si>
+    <t>133666005</t>
+  </si>
+  <si>
+    <t>133661314</t>
+  </si>
+  <si>
+    <t>133661408</t>
+  </si>
+  <si>
+    <t>133662817</t>
+  </si>
+  <si>
+    <t>133668943</t>
+  </si>
+  <si>
+    <t>133669484</t>
+  </si>
+  <si>
+    <t>133671420</t>
+  </si>
+  <si>
+    <t>133673604</t>
+  </si>
+  <si>
+    <t>133673675</t>
+  </si>
+  <si>
+    <t>Relatório de Recusas  04.08.2025 a 10.08.2025</t>
   </si>
 </sst>
 </file>
@@ -608,7 +533,7 @@
   <sheetPr>
     <pageSetUpPr autoPageBreaks="0"/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.7109375" style="1" customWidth="1" collapsed="1"/>
@@ -640,16 +565,16 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -658,16 +583,16 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>6</v>
@@ -676,16 +601,16 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>6</v>
@@ -694,16 +619,16 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>6</v>
@@ -712,16 +637,16 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>6</v>
@@ -730,16 +655,16 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>6</v>
@@ -748,16 +673,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>6</v>
@@ -766,16 +691,16 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E9" s="2" t="s">
         <v>6</v>
@@ -784,16 +709,16 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>6</v>
@@ -802,16 +727,16 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E11" s="2" t="s">
         <v>6</v>
@@ -820,16 +745,16 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>6</v>
@@ -838,16 +763,16 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E13" s="2" t="s">
         <v>6</v>
@@ -856,16 +781,16 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>6</v>
@@ -874,16 +799,16 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>6</v>
@@ -892,16 +817,16 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>6</v>
@@ -910,16 +835,16 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>6</v>
@@ -928,16 +853,16 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>7</v>
+        <v>9</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>32</v>
       </c>
       <c r="E18" s="2" t="s">
         <v>6</v>
@@ -945,16 +870,16 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>6</v>
@@ -962,16 +887,16 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E20" s="2" t="s">
         <v>6</v>
@@ -979,16 +904,16 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>6</v>
@@ -996,16 +921,16 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>6</v>
@@ -1013,16 +938,16 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>6</v>
@@ -1030,454 +955,23 @@
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D25" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D27" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D29" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B34" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B39" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B41" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B43" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B44" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B45" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D45" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D46" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D50" s="6"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D51" s="6"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D52" s="6"/>
+      <c r="D25" s="6"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
